--- a/data/performance/daily/signal_list_2026-06-09.xlsx
+++ b/data/performance/daily/signal_list_2026-06-09.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +41,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -74,6 +84,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -457,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-06-09</t>
+          <t>Swing — Review sesi market 2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 0.0%  (0W / 0L of 0 evaluated, 6 pending)</t>
+          <t>Win Rate: 71.4%  (5W / 2L of 7 evaluated)</t>
         </is>
       </c>
     </row>
@@ -523,45 +535,49 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CTTH.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v/>
+        <v>2020</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>2460</v>
       </c>
       <c r="E5" t="n">
-        <v/>
+        <v>2520</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v/>
+        <v>24.75</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
-      <c r="I5" t="n">
-        <v/>
+        <v>21.78</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>MLBI.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -570,29 +586,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v/>
+        <v>5925</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>5950</v>
       </c>
       <c r="E6" t="n">
-        <v/>
+        <v>6000</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v/>
+        <v>1.27</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
+        <v>0.42</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -608,29 +628,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v/>
+        <v>8050</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>8325</v>
       </c>
       <c r="E7" t="n">
-        <v/>
+        <v>8400</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v/>
+        <v>4.35</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H7" t="n">
-        <v/>
-      </c>
-      <c r="I7" t="n">
-        <v/>
+        <v>3.42</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -642,40 +666,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>PRE_MARKUP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v/>
+        <v>498</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>560</v>
       </c>
       <c r="E8" t="n">
-        <v/>
+        <v>570</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v/>
+        <v>14.46</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
+        <v>12.45</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MUTU.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -684,67 +712,117 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v/>
+        <v>168</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>143</v>
       </c>
       <c r="E9" t="n">
-        <v/>
+        <v>210</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v/>
+        <v>25</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="I9" t="n">
-        <v/>
+        <v>-14.88</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>MUTU.JK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>107</v>
+      </c>
+      <c r="D10" t="n">
+        <v>106</v>
+      </c>
+      <c r="E10" t="n">
+        <v>113</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>VISI.JK</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>PRE_MARKUP</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v/>
-      </c>
-      <c r="D10" t="n">
-        <v/>
-      </c>
-      <c r="E10" t="n">
-        <v/>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H10" t="n">
-        <v/>
-      </c>
-      <c r="I10" t="n">
-        <v/>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>pending</t>
+      <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1095</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1095</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -759,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -777,14 +855,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-06-09</t>
+          <t>Scalping — Review sesi market 2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 0.0%  (0W / 0L of 0 evaluated, 17 pending)</t>
+          <t>Win Rate: 33.3%  (4W / 8L of 12 evaluated)</t>
         </is>
       </c>
     </row>
@@ -843,7 +921,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALDO.JK</t>
+          <t>APLI.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -852,29 +930,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v/>
+        <v>288</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>252</v>
       </c>
       <c r="E5" t="n">
-        <v/>
+        <v>286</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v/>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H5" t="n">
-        <v/>
-      </c>
-      <c r="I5" t="n">
-        <v/>
+        <v>-12.5</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -890,36 +972,40 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v/>
+        <v>7450</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>6350</v>
       </c>
       <c r="E6" t="n">
-        <v/>
+        <v>6725</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v/>
+        <v>-9.73</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H6" t="n">
-        <v/>
-      </c>
-      <c r="I6" t="n">
-        <v/>
+        <v>-14.77</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FMII.JK</t>
+          <t>FORU.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -928,36 +1014,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v/>
+        <v>2020</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>2460</v>
       </c>
       <c r="E7" t="n">
-        <v/>
+        <v>2520</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v/>
+        <v>24.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H7" t="n">
-        <v/>
-      </c>
-      <c r="I7" t="n">
-        <v/>
+        <v>21.78</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FORU.JK</t>
+          <t>ICON.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -966,36 +1056,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v/>
+        <v>121</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>105</v>
       </c>
       <c r="E8" t="n">
-        <v/>
+        <v>122</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v/>
+        <v>0.83</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H8" t="n">
-        <v/>
-      </c>
-      <c r="I8" t="n">
-        <v/>
+        <v>-13.22</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SMMA.JK</t>
+          <t>TFCO.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1004,29 +1098,33 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v/>
+        <v>660</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>655</v>
       </c>
       <c r="E9" t="n">
-        <v/>
+        <v>655</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v/>
+        <v>-0.76</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H9" t="n">
-        <v/>
-      </c>
-      <c r="I9" t="n">
-        <v/>
+        <v>-0.76</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
@@ -1042,36 +1140,40 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v/>
+        <v>268</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>270</v>
       </c>
       <c r="E10" t="n">
-        <v/>
+        <v>278</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v/>
+        <v>3.73</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H10" t="n">
-        <v/>
-      </c>
-      <c r="I10" t="n">
-        <v/>
+        <v>0.75</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NZIA.JK</t>
+          <t>MSIN.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1080,36 +1182,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v/>
+        <v>580</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>570</v>
       </c>
       <c r="E11" t="n">
-        <v/>
+        <v>590</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v/>
+        <v>1.72</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H11" t="n">
-        <v/>
-      </c>
-      <c r="I11" t="n">
-        <v/>
+        <v>-1.72</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDO.JK</t>
+          <t>SATU.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,36 +1224,40 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v/>
+        <v>270</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>268</v>
       </c>
       <c r="E12" t="n">
-        <v/>
+        <v>272</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v/>
+        <v>0.74</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H12" t="n">
-        <v/>
-      </c>
-      <c r="I12" t="n">
-        <v/>
+        <v>-0.74</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MGLV.JK</t>
+          <t>NZIA.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1156,36 +1266,40 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v/>
+        <v>196</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>191</v>
       </c>
       <c r="E13" t="n">
-        <v/>
+        <v>226</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v/>
+        <v>15.31</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H13" t="n">
-        <v/>
-      </c>
-      <c r="I13" t="n">
-        <v/>
+        <v>-2.55</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADMR.JK</t>
+          <t>MGLV.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1194,36 +1308,40 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v/>
+        <v>8050</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>8325</v>
       </c>
       <c r="E14" t="n">
-        <v/>
+        <v>8400</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v/>
+        <v>4.35</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H14" t="n">
-        <v/>
-      </c>
-      <c r="I14" t="n">
-        <v/>
+        <v>3.42</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GULA.JK</t>
+          <t>GRIA.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1232,36 +1350,40 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v/>
+        <v>168</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>143</v>
       </c>
       <c r="E15" t="n">
-        <v/>
+        <v>210</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v/>
+        <v>25</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H15" t="n">
-        <v/>
-      </c>
-      <c r="I15" t="n">
-        <v/>
+        <v>-14.88</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MMIX.JK</t>
+          <t>VISI.JK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1270,219 +1392,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v/>
+        <v>1000</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>1095</v>
       </c>
       <c r="E16" t="n">
-        <v/>
+        <v>1095</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v/>
+        <v>9.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H16" t="n">
-        <v/>
-      </c>
-      <c r="I16" t="n">
-        <v/>
+        <v>9.5</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NAYZ.JK</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v/>
-      </c>
-      <c r="D17" t="n">
-        <v/>
-      </c>
-      <c r="E17" t="n">
-        <v/>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H17" t="n">
-        <v/>
-      </c>
-      <c r="I17" t="n">
-        <v/>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>GRIA.JK</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v/>
-      </c>
-      <c r="D18" t="n">
-        <v/>
-      </c>
-      <c r="E18" t="n">
-        <v/>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H18" t="n">
-        <v/>
-      </c>
-      <c r="I18" t="n">
-        <v/>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RSCH.JK</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v/>
-      </c>
-      <c r="D19" t="n">
-        <v/>
-      </c>
-      <c r="E19" t="n">
-        <v/>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H19" t="n">
-        <v/>
-      </c>
-      <c r="I19" t="n">
-        <v/>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AYAM.JK</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v/>
-      </c>
-      <c r="D20" t="n">
-        <v/>
-      </c>
-      <c r="E20" t="n">
-        <v/>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H20" t="n">
-        <v/>
-      </c>
-      <c r="I20" t="n">
-        <v/>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>VISI.JK</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SCALPING_HIGH</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v/>
-      </c>
-      <c r="D21" t="n">
-        <v/>
-      </c>
-      <c r="E21" t="n">
-        <v/>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v/>
-      </c>
-      <c r="H21" t="n">
-        <v/>
-      </c>
-      <c r="I21" t="n">
-        <v/>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>pending</t>
+          <t>evaluated</t>
         </is>
       </c>
     </row>

--- a/data/performance/daily/signal_list_2026-06-09.xlsx
+++ b/data/performance/daily/signal_list_2026-06-09.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-09.xlsx
+++ b/data/performance/daily/signal_list_2026-06-09.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-09.xlsx
+++ b/data/performance/daily/signal_list_2026-06-09.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -605,12 +616,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -689,12 +710,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-14.88</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>-0.93</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -815,12 +851,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -837,7 +878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -847,9 +888,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -879,7 +921,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -904,15 +946,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -949,12 +996,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -991,12 +1043,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1033,12 +1090,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,17 +1132,22 @@
       <c r="G8" s="4" t="n">
         <v>-13.22</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,12 +1184,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1159,12 +1231,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G11" s="4" t="n">
         <v>-1.72</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1238,17 +1320,22 @@
       <c r="G12" s="4" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1280,17 +1367,22 @@
       <c r="G13" s="4" t="n">
         <v>-2.55</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1327,12 +1419,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1364,17 +1461,22 @@
       <c r="G15" s="4" t="n">
         <v>-14.88</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1411,12 +1513,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-09.xlsx
+++ b/data/performance/daily/signal_list_2026-06-09.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>2020</v>
       </c>
       <c r="D5" t="n">
+        <v>2490</v>
+      </c>
+      <c r="E5" t="n">
         <v>2460</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2520</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>24.75</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>21.78</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>5925</v>
       </c>
       <c r="D6" t="n">
+        <v>5925</v>
+      </c>
+      <c r="E6" t="n">
         <v>5950</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>8050</v>
       </c>
       <c r="D7" t="n">
+        <v>7850</v>
+      </c>
+      <c r="E7" t="n">
         <v>8325</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>8400</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>4.35</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>3.42</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>498</v>
       </c>
       <c r="D8" t="n">
+        <v>496</v>
+      </c>
+      <c r="E8" t="n">
         <v>560</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>570</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>14.46</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>12.45</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>168</v>
       </c>
       <c r="D9" t="n">
+        <v>165</v>
+      </c>
+      <c r="E9" t="n">
         <v>143</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>210</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-14.88</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>107</v>
       </c>
       <c r="D10" t="n">
+        <v>113</v>
+      </c>
+      <c r="E10" t="n">
         <v>106</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>113</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>5.61</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.93</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>1000</v>
       </c>
       <c r="D11" t="n">
-        <v>1095</v>
+        <v>1040</v>
       </c>
       <c r="E11" t="n">
         <v>1095</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>9.5</v>
+      <c r="F11" t="n">
+        <v>1095</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>9.5</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H11" s="4" t="n">
+        <v>9.5</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -878,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -886,12 +913,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,45 +949,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -980,33 +1013,36 @@
         <v>288</v>
       </c>
       <c r="D5" t="n">
+        <v>246</v>
+      </c>
+      <c r="E5" t="n">
         <v>252</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>286</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1027,33 +1063,36 @@
         <v>7450</v>
       </c>
       <c r="D6" t="n">
+        <v>6450</v>
+      </c>
+      <c r="E6" t="n">
         <v>6350</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6725</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>-9.73</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-14.77</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1074,33 +1113,36 @@
         <v>2020</v>
       </c>
       <c r="D7" t="n">
+        <v>2490</v>
+      </c>
+      <c r="E7" t="n">
         <v>2460</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2520</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>24.75</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>21.78</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1121,33 +1163,36 @@
         <v>121</v>
       </c>
       <c r="D8" t="n">
+        <v>118</v>
+      </c>
+      <c r="E8" t="n">
         <v>105</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>122</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-13.22</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1173,28 +1218,31 @@
       <c r="E9" t="n">
         <v>655</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>-0.76</v>
+      <c r="F9" t="n">
+        <v>655</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="4" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>268</v>
       </c>
       <c r="D10" t="n">
+        <v>266</v>
+      </c>
+      <c r="E10" t="n">
         <v>270</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>278</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>3.73</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>580</v>
       </c>
       <c r="D11" t="n">
+        <v>580</v>
+      </c>
+      <c r="E11" t="n">
         <v>570</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>590</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>1.72</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-1.72</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>270</v>
       </c>
       <c r="D12" t="n">
+        <v>270</v>
+      </c>
+      <c r="E12" t="n">
         <v>268</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>272</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>196</v>
       </c>
       <c r="D13" t="n">
+        <v>169</v>
+      </c>
+      <c r="E13" t="n">
         <v>191</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>226</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>15.31</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-2.55</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>8050</v>
       </c>
       <c r="D14" t="n">
+        <v>7850</v>
+      </c>
+      <c r="E14" t="n">
         <v>8325</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>8400</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>4.35</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>3.42</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>168</v>
       </c>
       <c r="D15" t="n">
+        <v>165</v>
+      </c>
+      <c r="E15" t="n">
         <v>143</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>210</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-14.88</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>1000</v>
       </c>
       <c r="D16" t="n">
-        <v>1095</v>
+        <v>1040</v>
       </c>
       <c r="E16" t="n">
         <v>1095</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>9.5</v>
+      <c r="F16" t="n">
+        <v>1095</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>9.5</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H16" s="4" t="n">
+        <v>9.5</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
